--- a/reviews/a-envoyer/jlawsongolf-2026-09-21.xlsx
+++ b/reviews/a-envoyer/jlawsongolf-2026-09-21.xlsx
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-18T06:05:16</t>
+          <t>2026-09-18T09:30:42</t>
         </is>
       </c>
     </row>
